--- a/Budweg/BD_Projekt/Medarbejder.xlsx
+++ b/Budweg/BD_Projekt/Medarbejder.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MPH\Programmering\2.Semster\Budweg\BD_Projekt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MPH\Programmering\2.Semster\Budweg_TeamB2\Budweg\BD_Projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CAAB139-11DE-4225-A890-317A87ADB35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48191284-7966-4142-837B-FEC4300E91A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3612" yWindow="3540" windowWidth="17280" windowHeight="9420" xr2:uid="{AE2671BC-EED1-4FE4-8DD8-FB44C93CE05B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{AE2671BC-EED1-4FE4-8DD8-FB44C93CE05B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,47 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>stationsID</t>
   </si>
   <si>
-    <t>Bob</t>
-  </si>
-  <si>
-    <t>Operator</t>
-  </si>
-  <si>
-    <t>Tom</t>
-  </si>
-  <si>
-    <t>Kim</t>
-  </si>
-  <si>
-    <t>Eva</t>
-  </si>
-  <si>
-    <t>Supervisor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas </t>
-  </si>
-  <si>
-    <t>hansen</t>
-  </si>
-  <si>
-    <t>jensen</t>
-  </si>
-  <si>
-    <t>Bondegård</t>
-  </si>
-  <si>
-    <t>Holbæk</t>
-  </si>
-  <si>
-    <t>Brown</t>
-  </si>
-  <si>
     <t>WorkorderID</t>
   </si>
   <si>
@@ -87,6 +51,12 @@
   </si>
   <si>
     <t>role</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -499,105 +469,65 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1">
-        <v>6</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="1">
-        <v>3</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1">
-        <v>10</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="1">
-        <v>11</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
